--- a/lang/ar/headTags.xlsx
+++ b/lang/ar/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1209</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2395">
   <si>
     <t>en</t>
   </si>
@@ -5755,6 +5755,18 @@
     <t>شولكر</t>
   </si>
   <si>
+    <t>Sift (Inspired)</t>
+  </si>
+  <si>
+    <t>Sift (مستوحى)</t>
+  </si>
+  <si>
+    <t>Sift (Vanilla)</t>
+  </si>
+  <si>
+    <t>Sift (الفانيليا)</t>
+  </si>
+  <si>
     <t>Silent Hill</t>
   </si>
   <si>
@@ -6664,6 +6676,12 @@
     <t>ULTRAKILL</t>
   </si>
   <si>
+    <t>Umamusume</t>
+  </si>
+  <si>
+    <t>أوماموسومي</t>
+  </si>
+  <si>
     <t>Umineko - When They Cry</t>
   </si>
   <si>
@@ -6953,6 +6971,12 @@
   </si>
   <si>
     <t>وينتر</t>
+  </si>
+  <si>
+    <t>Winter Drop</t>
+  </si>
+  <si>
+    <t>مجموعة الشتاء</t>
   </si>
   <si>
     <t>Witcher</t>
@@ -7524,7 +7548,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1205"/>
+  <dimension ref="A1:B1209"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15712,20 +15736,20 @@
         <v>2032</v>
       </c>
       <c r="B1023" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="B1024" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="B1025" t="s">
         <v>2036</v>
@@ -15992,20 +16016,20 @@
         <v>2101</v>
       </c>
       <c r="B1058" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="B1059" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="B1060" t="s">
         <v>2105</v>
@@ -16024,20 +16048,20 @@
         <v>2108</v>
       </c>
       <c r="B1062" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="B1063" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="B1064" t="s">
         <v>2112</v>
@@ -16064,20 +16088,20 @@
         <v>2117</v>
       </c>
       <c r="B1067" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="B1068" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="B1069" t="s">
         <v>2121</v>
@@ -16192,20 +16216,20 @@
         <v>2148</v>
       </c>
       <c r="B1083" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="B1084" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="B1085" t="s">
         <v>2152</v>
@@ -16360,23 +16384,23 @@
         <v>2189</v>
       </c>
       <c r="B1104" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="B1105" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1106" t="s">
         <v>2192</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>2193</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
@@ -16464,20 +16488,20 @@
         <v>2214</v>
       </c>
       <c r="B1117" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="B1118" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="B1119" t="s">
         <v>2218</v>
@@ -16496,28 +16520,28 @@
         <v>2221</v>
       </c>
       <c r="B1121" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="B1122" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="B1123" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="B1124" t="s">
         <v>2227</v>
@@ -16528,28 +16552,28 @@
         <v>2228</v>
       </c>
       <c r="B1125" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="B1126" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="B1127" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="B1128" t="s">
         <v>2234</v>
@@ -16776,28 +16800,28 @@
         <v>2289</v>
       </c>
       <c r="B1156" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="B1157" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="B1158" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="B1159" t="s">
         <v>2295</v>
@@ -17104,39 +17128,39 @@
         <v>2370</v>
       </c>
       <c r="B1197" t="s">
-        <v>922</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="B1198" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="B1199" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="B1200" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="B1201" t="s">
-        <v>2378</v>
+        <v>922</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
@@ -17171,8 +17195,40 @@
         <v>2386</v>
       </c>
     </row>
+    <row r="1206" spans="1:2">
+      <c r="A1206" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B1206" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2">
+      <c r="A1207" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2">
+      <c r="A1208" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2">
+      <c r="A1209" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>2394</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1205"/>
+  <autoFilter ref="A1:B1209"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
